--- a/data/trans_orig/IP22D3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Estudios-trans_orig.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29477</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>35190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63562</t>
+          <t>63383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>40870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>46866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>38614</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49072</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82183</t>
+          <t>82292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94239</t>
+          <t>94198</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D3_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>32,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>19,69%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>87,34%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -838,34 +838,34 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>67,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>783</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29470</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>27092</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28312</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35190</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,22 +1477,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>57289</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55008</t>
+          <t>52612</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63383</t>
+          <t>60747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -1515,107 +1515,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3919</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5368</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5710</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2552</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5145</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2659</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2660</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6147</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -1971,74 +1971,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8568</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>75,08%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>43,77%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>8975</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>7104</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>72,77%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9235</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7364</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>74,71%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>8094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>4607</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>10088</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>42,84%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13022</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7296</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>40483</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>34183</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44487</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>83,47%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>70,48%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>44630</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>40870</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>46866</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>84,85%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>80123</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82292</t>
+          <t>73751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94198</t>
+          <t>84883</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -2653,107 +2653,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>4806</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -2766,107 +2766,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2494</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
